--- a/ressource/rattachement PLF.xlsx
+++ b/ressource/rattachement PLF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://transgourmetfr-my.sharepoint.com/personal/tristan_ngounou_transgourmet_fr/Documents/Desktop/Samsara Reporting/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://transgourmetfr-my.sharepoint.com/personal/tristan_ngounou_transgourmet_fr/Documents/Desktop/Samsara Reporting/ressource/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="8_{5B98D222-027F-4399-ACB9-FFF057EAFF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23FAEF5C-6167-401B-AB73-A0142F725F6B}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{161B35AD-3003-4E5C-9D11-4507845B2A91}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{161B35AD-3003-4E5C-9D11-4507845B2A91}"/>
   </bookViews>
   <sheets>
     <sheet name="rattachement PF" sheetId="1" r:id="rId1"/>
@@ -582,7 +582,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
@@ -593,19 +593,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -926,10 +917,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -940,10 +931,10 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -951,10 +942,10 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -965,10 +956,10 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -976,10 +967,10 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -990,10 +981,10 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -1004,10 +995,10 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -1018,10 +1009,10 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -1032,10 +1023,10 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C9" s="4" t="s">
@@ -1046,10 +1037,10 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -1060,10 +1051,10 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -1074,10 +1065,10 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -1088,10 +1079,10 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -1102,10 +1093,10 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -1116,10 +1107,10 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="4" t="s">
@@ -1130,10 +1121,10 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -1144,10 +1135,10 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C17" s="4" t="s">
@@ -1158,10 +1149,10 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C18" s="4" t="s">
@@ -1172,10 +1163,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="4" t="s">
@@ -1186,10 +1177,10 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -1200,10 +1191,10 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C21" s="4" t="s">
@@ -1214,10 +1205,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -1228,906 +1219,906 @@
       </c>
     </row>
     <row r="23" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C25"/>
     </row>
     <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C26"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C27"/>
     </row>
     <row r="28" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C28"/>
     </row>
     <row r="29" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C29"/>
     </row>
     <row r="30" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C30"/>
     </row>
     <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C31"/>
     </row>
     <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C32"/>
     </row>
     <row r="33" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C33"/>
     </row>
     <row r="34" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="12" t="s">
+      <c r="A34" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C34"/>
     </row>
     <row r="35" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C35"/>
     </row>
     <row r="36" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C36"/>
     </row>
     <row r="37" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C37"/>
     </row>
     <row r="38" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C38"/>
     </row>
     <row r="39" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C39"/>
     </row>
     <row r="40" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="3" t="s">
         <v>41</v>
       </c>
       <c r="C40"/>
     </row>
     <row r="41" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C41"/>
     </row>
     <row r="42" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C42"/>
     </row>
     <row r="43" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C43"/>
     </row>
     <row r="44" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C44"/>
     </row>
     <row r="45" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A45" s="12" t="s">
+      <c r="A45" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C45"/>
     </row>
     <row r="46" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A46" s="12" t="s">
+      <c r="A46" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C46"/>
     </row>
     <row r="47" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A47" s="12" t="s">
+      <c r="A47" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C47"/>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="12" t="s">
+      <c r="A48" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B48" s="6"/>
+      <c r="B48"/>
       <c r="C48"/>
     </row>
     <row r="49" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="12" t="s">
+      <c r="A49" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C49"/>
     </row>
     <row r="50" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A50" s="15" t="s">
+      <c r="A50" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B50" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C50"/>
     </row>
     <row r="51" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A51" s="12" t="s">
+      <c r="A51" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="B51" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C51"/>
     </row>
     <row r="52" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="15" t="s">
+      <c r="A52" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C52"/>
     </row>
     <row r="53" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C53"/>
     </row>
     <row r="54" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A54" s="15" t="s">
+      <c r="A54" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C54"/>
     </row>
     <row r="55" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A55" s="7" t="s">
+      <c r="A55" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B55" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C55"/>
     </row>
     <row r="56" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A56" s="7" t="s">
+      <c r="A56" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C56"/>
     </row>
     <row r="57" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A57" s="7" t="s">
+      <c r="A57" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C57"/>
     </row>
     <row r="58" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A58" s="14" t="s">
+      <c r="A58" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C58"/>
     </row>
     <row r="59" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A59" s="12" t="s">
+      <c r="A59" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B59" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C59"/>
     </row>
     <row r="60" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A60" s="12" t="s">
+      <c r="A60" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C60"/>
     </row>
     <row r="61" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A61" s="7" t="s">
+      <c r="A61" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B61" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C61"/>
     </row>
     <row r="62" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A62" s="7" t="s">
+      <c r="A62" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C62"/>
     </row>
     <row r="63" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A63" s="7" t="s">
+      <c r="A63" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B63" s="9" t="s">
+      <c r="B63" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C63"/>
     </row>
     <row r="64" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A64" s="7" t="s">
+      <c r="A64" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="3" t="s">
         <v>41</v>
       </c>
       <c r="C64"/>
     </row>
     <row r="65" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A65" s="7" t="s">
+      <c r="A65" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C65"/>
     </row>
     <row r="66" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A66" s="12" t="s">
+      <c r="A66" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B66" s="9" t="s">
+      <c r="B66" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C66"/>
     </row>
     <row r="67" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A67" s="12" t="s">
+      <c r="A67" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B67" s="9" t="s">
+      <c r="B67" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C67"/>
     </row>
     <row r="68" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A68" s="14" t="s">
+      <c r="A68" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="B68" s="9" t="s">
+      <c r="B68" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C68"/>
     </row>
     <row r="69" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B69" s="10" t="s">
+      <c r="B69" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C69"/>
     </row>
     <row r="70" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A70" s="13" t="s">
+      <c r="A70" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B70" s="10" t="s">
+      <c r="B70" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C70"/>
     </row>
     <row r="71" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A71" s="13" t="s">
+      <c r="A71" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="B71" s="10" t="s">
+      <c r="B71" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C71"/>
     </row>
     <row r="72" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A72" s="13" t="s">
+      <c r="A72" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="B72" s="9" t="s">
+      <c r="B72" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C72"/>
     </row>
     <row r="73" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A73" s="13" t="s">
+      <c r="A73" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B73" s="9" t="s">
+      <c r="B73" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C73"/>
     </row>
     <row r="74" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A74" s="8" t="s">
+      <c r="A74" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B74" s="10" t="s">
+      <c r="B74" s="5" t="s">
         <v>47</v>
       </c>
       <c r="C74"/>
     </row>
     <row r="75" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A75" s="13" t="s">
+      <c r="A75" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B75" s="10" t="s">
+      <c r="B75" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C75"/>
     </row>
     <row r="76" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A76" s="13" t="s">
+      <c r="A76" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="B76" s="9" t="s">
+      <c r="B76" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C76"/>
     </row>
     <row r="77" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B77" s="10" t="s">
+      <c r="B77" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C77"/>
     </row>
     <row r="78" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A78" s="11" t="s">
+      <c r="A78" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="B78" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C78"/>
     </row>
     <row r="79" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A79" s="13" t="s">
+      <c r="A79" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="B79" s="9" t="s">
+      <c r="B79" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C79"/>
     </row>
     <row r="80" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A80" s="8" t="s">
+      <c r="A80" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B80" s="9" t="s">
+      <c r="B80" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C80"/>
     </row>
     <row r="81" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A81" s="11" t="s">
+      <c r="A81" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B81" s="9" t="s">
+      <c r="B81" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C81"/>
     </row>
     <row r="82" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A82" s="13" t="s">
+      <c r="A82" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="B82" s="9" t="s">
+      <c r="B82" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C82"/>
     </row>
     <row r="83" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A83" s="8" t="s">
+      <c r="A83" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B83" s="9" t="s">
+      <c r="B83" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C83"/>
     </row>
     <row r="84" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A84" s="13" t="s">
+      <c r="A84" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="B84" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C84"/>
     </row>
     <row r="85" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A85" s="13" t="s">
+      <c r="A85" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="B85" s="10" t="s">
+      <c r="B85" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C85"/>
     </row>
     <row r="86" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A86" s="8" t="s">
+      <c r="A86" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B86" s="10" t="s">
+      <c r="B86" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C86"/>
     </row>
     <row r="87" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A87" s="8" t="s">
+      <c r="A87" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B87" s="9" t="s">
+      <c r="B87" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C87"/>
     </row>
     <row r="88" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A88" s="13" t="s">
+      <c r="A88" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="B88" s="10" t="s">
+      <c r="B88" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C88"/>
     </row>
     <row r="89" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A89" s="8" t="s">
+      <c r="A89" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B89" s="10" t="s">
+      <c r="B89" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C89"/>
     </row>
     <row r="90" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A90" s="13" t="s">
+      <c r="A90" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="B90" s="9" t="s">
+      <c r="B90" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C90"/>
     </row>
     <row r="91" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A91" s="13" t="s">
+      <c r="A91" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="B91" s="9" t="s">
+      <c r="B91" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C91"/>
     </row>
     <row r="92" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A92" s="13" t="s">
+      <c r="A92" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B92" s="9" t="s">
+      <c r="B92" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C92"/>
     </row>
     <row r="93" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A93" s="13" t="s">
+      <c r="A93" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B93" s="9" t="s">
+      <c r="B93" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C93"/>
     </row>
     <row r="94" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A94" s="11" t="s">
+      <c r="A94" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B94" s="9" t="s">
+      <c r="B94" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C94"/>
     </row>
     <row r="95" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A95" s="13" t="s">
+      <c r="A95" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="B95" s="10" t="s">
+      <c r="B95" s="5" t="s">
         <v>61</v>
       </c>
       <c r="C95"/>
     </row>
     <row r="96" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A96" s="13" t="s">
+      <c r="A96" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B96" s="9" t="s">
+      <c r="B96" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C96"/>
     </row>
     <row r="97" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A97" s="11" t="s">
+      <c r="A97" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="B97" s="9" t="s">
+      <c r="B97" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C97"/>
     </row>
     <row r="98" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A98" s="13" t="s">
+      <c r="A98" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B98" s="9" t="s">
+      <c r="B98" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C98"/>
     </row>
     <row r="99" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A99" s="13" t="s">
+      <c r="A99" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="B99" s="9" t="s">
+      <c r="B99" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C99"/>
     </row>
     <row r="100" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A100" s="13" t="s">
+      <c r="A100" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="B100" s="10" t="s">
+      <c r="B100" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C100"/>
     </row>
     <row r="101" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A101" s="13" t="s">
+      <c r="A101" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="B101" s="9" t="s">
+      <c r="B101" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C101"/>
     </row>
     <row r="102" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A102" s="13" t="s">
+      <c r="A102" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B102" s="9" t="s">
+      <c r="B102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C102"/>
     </row>
     <row r="103" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A103" s="13" t="s">
+      <c r="A103" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B103" s="9" t="s">
+      <c r="B103" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C103"/>
     </row>
     <row r="104" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A104" s="13" t="s">
+      <c r="A104" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="B104" s="10" t="s">
+      <c r="B104" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C104"/>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A105" s="8" t="s">
+      <c r="A105" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B105" s="8" t="s">
+      <c r="B105" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C105"/>
     </row>
     <row r="106" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A106" s="8" t="s">
+      <c r="A106" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B106" s="10" t="s">
+      <c r="B106" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C106"/>
     </row>
     <row r="107" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A107" s="8" t="s">
+      <c r="A107" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B107" s="10" t="s">
+      <c r="B107" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C107"/>
     </row>
     <row r="108" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A108" s="8" t="s">
+      <c r="A108" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B108" s="9" t="s">
+      <c r="B108" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C108"/>
     </row>
     <row r="109" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A109" s="8" t="s">
+      <c r="A109" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B109" s="9" t="s">
+      <c r="B109" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C109"/>
     </row>
     <row r="110" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A110" s="6" t="s">
+      <c r="A110" t="s">
         <v>137</v>
       </c>
-      <c r="B110" s="10" t="s">
+      <c r="B110" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C110"/>
     </row>
     <row r="111" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A111" s="6" t="s">
+      <c r="A111" t="s">
         <v>138</v>
       </c>
-      <c r="B111" s="9" t="s">
+      <c r="B111" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C111"/>
     </row>
     <row r="112" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A112" s="6" t="s">
+      <c r="A112" t="s">
         <v>139</v>
       </c>
-      <c r="B112" s="9" t="s">
+      <c r="B112" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C112"/>
     </row>
     <row r="113" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A113" s="6" t="s">
+      <c r="A113" t="s">
         <v>140</v>
       </c>
-      <c r="B113" s="9" t="s">
+      <c r="B113" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C113"/>
     </row>
     <row r="114" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A114" s="6" t="s">
+      <c r="A114" t="s">
         <v>141</v>
       </c>
-      <c r="B114" s="10" t="s">
+      <c r="B114" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C114"/>
     </row>
     <row r="115" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A115" s="6" t="s">
+      <c r="A115" t="s">
         <v>142</v>
       </c>
-      <c r="B115" s="10" t="s">
+      <c r="B115" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C115"/>
     </row>
     <row r="116" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A116" s="6" t="s">
+      <c r="A116" t="s">
         <v>143</v>
       </c>
-      <c r="B116" s="9" t="s">
+      <c r="B116" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C116"/>
     </row>
     <row r="117" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A117" s="6" t="s">
+      <c r="A117" t="s">
         <v>144</v>
       </c>
-      <c r="B117" s="9" t="s">
+      <c r="B117" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C117"/>
     </row>
     <row r="118" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A118" s="6" t="s">
+      <c r="A118" t="s">
         <v>145</v>
       </c>
-      <c r="B118" s="9" t="s">
+      <c r="B118" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C118"/>
     </row>
     <row r="119" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A119" s="6" t="s">
+      <c r="A119" t="s">
         <v>146</v>
       </c>
-      <c r="B119" s="9" t="s">
+      <c r="B119" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C119"/>
     </row>
     <row r="120" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A120" s="6" t="s">
+      <c r="A120" t="s">
         <v>147</v>
       </c>
-      <c r="B120" s="9" t="s">
+      <c r="B120" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C120"/>
     </row>
     <row r="121" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A121" s="6" t="s">
+      <c r="A121" t="s">
         <v>148</v>
       </c>
-      <c r="B121" s="10" t="s">
+      <c r="B121" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C121"/>
     </row>
     <row r="122" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A122" s="6" t="s">
+      <c r="A122" t="s">
         <v>149</v>
       </c>
-      <c r="B122" s="9" t="s">
+      <c r="B122" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C122"/>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A123" s="8" t="s">
+      <c r="A123" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B123" s="8" t="s">
+      <c r="B123" s="1" t="s">
         <v>151</v>
       </c>
       <c r="C123"/>
